--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/delete-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/delete-bbt-form.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="68">
   <si>
     <t>Statement: UserRepository.delete(id) – deletes the parent User cascading to profile.</t>
   </si>
@@ -136,7 +136,10 @@
     <t>id = ""</t>
   </si>
   <si>
-    <t>id = "a"</t>
+    <t>id = "a" (inex)</t>
+  </si>
+  <si>
+    <t>id = "a" (exist)</t>
   </si>
   <si>
     <t>BVA</t>
@@ -145,7 +148,13 @@
     <t>BVA-1 Empty</t>
   </si>
   <si>
-    <t>BVA-2 OneChar</t>
+    <t>BVA-2 InexChar</t>
+  </si>
+  <si>
+    <t>BVA-3 ExistChar</t>
+  </si>
+  <si>
+    <t>Resolves successfully</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -167,6 +176,9 @@
   </si>
   <si>
     <t>BVA-2</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
   </si>
   <si>
     <t>Testing</t>
@@ -882,7 +894,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -923,6 +935,17 @@
         <v>39</v>
       </c>
     </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -931,7 +954,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -946,7 +969,7 @@
         <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>23</v>
@@ -963,7 +986,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>38</v>
@@ -980,7 +1003,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>39</v>
@@ -989,6 +1012,23 @@
         <v>34</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1000,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1016,10 +1056,10 @@
         <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>23</v>
@@ -1042,7 +1082,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>28</v>
@@ -1062,7 +1102,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>28</v>
@@ -1082,7 +1122,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>34</v>
@@ -1099,7 +1139,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>38</v>
@@ -1119,7 +1159,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>39</v>
@@ -1128,6 +1168,26 @@
         <v>34</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1156,16 +1216,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1173,45 +1233,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F2" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="J2" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B3" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1220,19 +1280,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/delete-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/delete-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="68">
-  <si>
-    <t>Statement: UserRepository.delete(id) – deletes the parent User cascading to profile.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="60">
+  <si>
+    <t>Statement: UserRepository.delete(id) – Deletes the user record and their associated profile (member or admin). Checks both tables to locate the record. Returns void on success. Throws NotFoundError if neither a member nor an admin exists with the given ID.</t>
   </si>
   <si>
     <t/>
@@ -37,19 +37,19 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible</t>
+    <t>Database is accessible. The ID may belong to a member, an admin, or neither.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;void&gt; | throws NotFoundError</t>
+    <t>Output: Promise&lt;void&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>User and profile records deleted.</t>
+    <t>On success: promise resolves to undefined (void). On failure: NotFoundError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,22 +64,16 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>MemberId input</t>
-  </si>
-  <si>
-    <t>id is an existing memberId</t>
-  </si>
-  <si>
-    <t>AdminId input</t>
-  </si>
-  <si>
-    <t>id is an existing adminId</t>
-  </si>
-  <si>
-    <t>Non-existent</t>
-  </si>
-  <si>
-    <t>ID not found (NotFoundError)</t>
+    <t>User type</t>
+  </si>
+  <si>
+    <t>Existing member ID → resolves void</t>
+  </si>
+  <si>
+    <t>Existing admin ID → resolves void</t>
+  </si>
+  <si>
+    <t>Non-existent ID (no member, no admin) → NotFoundError</t>
   </si>
   <si>
     <t>No TC</t>
@@ -100,10 +94,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>Existing memberId</t>
-  </si>
-  <si>
-    <t>Resolves void</t>
+    <t>id: MEMBER_ID (member exists, admin: null)</t>
+  </si>
+  <si>
+    <t>resolves void</t>
   </si>
   <si>
     <t>Passed</t>
@@ -112,16 +106,16 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Existing adminId</t>
+    <t>id: ADMIN_ID (member: null, admin exists)</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>Non-existent ID</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
+    <t>id: NONEXISTENT_ID (member: null, admin: null)</t>
+  </si>
+  <si>
+    <t>throws NotFoundError</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -133,28 +127,25 @@
     <t>ID length</t>
   </si>
   <si>
-    <t>id = ""</t>
-  </si>
-  <si>
-    <t>id = "a" (inex)</t>
-  </si>
-  <si>
-    <t>id = "a" (exist)</t>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found as member)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Empty</t>
-  </si>
-  <si>
-    <t>BVA-2 InexChar</t>
-  </si>
-  <si>
-    <t>BVA-3 ExistChar</t>
-  </si>
-  <si>
-    <t>Resolves successfully</t>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>id: "" (member: null, admin: null)</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>id: "a" (no match in member or admin)</t>
+  </si>
+  <si>
+    <t>id: "a" (member found: { ...MOCK_MEMBER_WITH_USER, id: "a" })</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -163,24 +154,9 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>MemberId delete</t>
-  </si>
-  <si>
-    <t>AdminId delete</t>
-  </si>
-  <si>
-    <t>Non-existent id</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>BVA-2</t>
-  </si>
-  <si>
-    <t>BVA-3</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -211,7 +187,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>MEM-01/AUTH-06</t>
+    <t>REPO-12</t>
   </si>
   <si>
     <t>n/a</t>
@@ -777,10 +753,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
@@ -791,13 +767,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -820,19 +796,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -840,16 +816,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -857,16 +833,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -874,16 +850,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -894,7 +870,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -904,13 +880,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,32 +894,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -966,19 +920,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -986,16 +940,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1003,16 +957,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1020,16 +974,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1053,22 +1007,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1076,19 +1030,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1096,19 +1050,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1116,19 +1070,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1139,16 +1093,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1159,16 +1113,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1179,16 +1133,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1216,16 +1170,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1233,39 +1187,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1">
         <v>6</v>
@@ -1280,19 +1234,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
